--- a/docs/handouts/chapter_1_5_handout.xlsx
+++ b/docs/handouts/chapter_1_5_handout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RussellStuff\Time series personal work\timeseries\handouts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7456007-9217-492C-A54C-2E211A1721FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56789BC9-1F85-4027-B672-BC14645CC5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
@@ -35,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
   <si>
     <t>Year</t>
   </si>
@@ -50,9 +72,6 @@
     <t>2005 Q1</t>
   </si>
   <si>
-    <t>______</t>
-  </si>
-  <si>
     <t>2005 Q2</t>
   </si>
   <si>
@@ -90,9 +109,6 @@
   </si>
   <si>
     <t>2008 Q2</t>
-  </si>
-  <si>
-    <t>⋮</t>
   </si>
   <si>
     <t>2022 Q4</t>
@@ -117,46 +133,254 @@
     <t>Quarter</t>
   </si>
   <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonally Adjusted </t>
+  </si>
+  <si>
     <t>Table 1: Computation of the 
-Centered Moving Average,      , and the Estimated Quarterly Multiplicative Effect,</t>
-  </si>
-  <si>
-    <t>Table 2: Computation of Seasonally Adjusted Factors</t>
-  </si>
-  <si>
-    <t> ______</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>Q4</t>
-  </si>
-  <si>
-    <t>Overall
-Mean</t>
-  </si>
-  <si>
-    <t>Random</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seasonally Adjusted </t>
+Centered Moving Average,             , and the Estimated Quarterly Multiplicative Effect,</t>
+  </si>
+  <si>
+    <t>Table 2: Computation of Seasonally Adjusted Factors,</t>
+  </si>
+  <si>
+    <t>2008 Q3</t>
+  </si>
+  <si>
+    <t>2008 Q4</t>
+  </si>
+  <si>
+    <t>2009 Q1</t>
+  </si>
+  <si>
+    <t>2009 Q2</t>
+  </si>
+  <si>
+    <t>2009 Q3</t>
+  </si>
+  <si>
+    <t>2009 Q4</t>
+  </si>
+  <si>
+    <t>2010 Q1</t>
+  </si>
+  <si>
+    <t>2010 Q2</t>
+  </si>
+  <si>
+    <t>2010 Q3</t>
+  </si>
+  <si>
+    <t>2010 Q4</t>
+  </si>
+  <si>
+    <t>2011 Q1</t>
+  </si>
+  <si>
+    <t>2011 Q2</t>
+  </si>
+  <si>
+    <t>2011 Q3</t>
+  </si>
+  <si>
+    <t>2011 Q4</t>
+  </si>
+  <si>
+    <t>2012 Q1</t>
+  </si>
+  <si>
+    <t>2012 Q2</t>
+  </si>
+  <si>
+    <t>2012 Q3</t>
+  </si>
+  <si>
+    <t>2012 Q4</t>
+  </si>
+  <si>
+    <t>2013 Q1</t>
+  </si>
+  <si>
+    <t>2013 Q2</t>
+  </si>
+  <si>
+    <t>2013 Q3</t>
+  </si>
+  <si>
+    <t>2013 Q4</t>
+  </si>
+  <si>
+    <t>2014 Q1</t>
+  </si>
+  <si>
+    <t>2014 Q2</t>
+  </si>
+  <si>
+    <t>2014 Q3</t>
+  </si>
+  <si>
+    <t>2014 Q4</t>
+  </si>
+  <si>
+    <t>2015 Q1</t>
+  </si>
+  <si>
+    <t>2015 Q2</t>
+  </si>
+  <si>
+    <t>2015 Q3</t>
+  </si>
+  <si>
+    <t>2015 Q4</t>
+  </si>
+  <si>
+    <t>2016 Q1</t>
+  </si>
+  <si>
+    <t>2016 Q2</t>
+  </si>
+  <si>
+    <t>2016 Q3</t>
+  </si>
+  <si>
+    <t>2016 Q4</t>
+  </si>
+  <si>
+    <t>2017 Q1</t>
+  </si>
+  <si>
+    <t>2017 Q2</t>
+  </si>
+  <si>
+    <t>2017 Q3</t>
+  </si>
+  <si>
+    <t>2017 Q4</t>
+  </si>
+  <si>
+    <t>2018 Q1</t>
+  </si>
+  <si>
+    <t>2018 Q2</t>
+  </si>
+  <si>
+    <t>2018 Q3</t>
+  </si>
+  <si>
+    <t>2018 Q4</t>
+  </si>
+  <si>
+    <t>2019 Q1</t>
+  </si>
+  <si>
+    <t>2019 Q2</t>
+  </si>
+  <si>
+    <t>2019 Q3</t>
+  </si>
+  <si>
+    <t>2019 Q4</t>
+  </si>
+  <si>
+    <t>2020 Q1</t>
+  </si>
+  <si>
+    <t>2020 Q2</t>
+  </si>
+  <si>
+    <t>2020 Q3</t>
+  </si>
+  <si>
+    <t>2020 Q4</t>
+  </si>
+  <si>
+    <t>2021 Q1</t>
+  </si>
+  <si>
+    <t>2021 Q2</t>
+  </si>
+  <si>
+    <t>2021 Q3</t>
+  </si>
+  <si>
+    <t>2021 Q4</t>
+  </si>
+  <si>
+    <t>2022 Q1</t>
+  </si>
+  <si>
+    <t>2022 Q2</t>
+  </si>
+  <si>
+    <t>2022 Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>2024 Q1</t>
+  </si>
+  <si>
+    <t>2024 Q2</t>
+  </si>
+  <si>
+    <t>2024 Q3</t>
+  </si>
+  <si>
+    <t>2024 Q4</t>
+  </si>
+  <si>
+    <t>2025 Q1</t>
+  </si>
+  <si>
+    <t>2025 Q2</t>
+  </si>
+  <si>
+    <t>2025 Q3</t>
+  </si>
+  <si>
+    <t>2025 Q4</t>
+  </si>
+  <si>
+    <t>2026 Q1</t>
+  </si>
+  <si>
+    <t>2026 Q2</t>
+  </si>
+  <si>
+    <t>2026 Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Mean, </t>
+  </si>
+  <si>
+    <t>Table 3:  Computation of the Estimate of the Random 
+Component and the Seasonally Adjusted Time Series</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,32 +397,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color rgb="FF000000"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9.6"/>
-      <color theme="1"/>
-      <name val="Source Sans Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
@@ -206,7 +404,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -227,18 +425,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -268,19 +460,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -339,118 +518,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -464,143 +531,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -618,237 +554,96 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -873,7 +668,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
@@ -978,10 +773,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1126,15 +918,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -1143,7 +932,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -1292,15 +1081,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -1309,7 +1095,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -1408,8 +1194,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
     <xdr:sp macro="" textlink="">
@@ -1463,7 +1249,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
@@ -1513,14 +1299,11 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -1530,7 +1313,7 @@
                           <m:accPr>
                             <m:chr m:val="̅"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -1623,7 +1406,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180819" cy="231923"/>
@@ -1642,7 +1425,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="381000" y="9269730"/>
+              <a:off x="381000" y="22225000"/>
               <a:ext cx="180819" cy="231923"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1673,10 +1456,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̅"/>
@@ -1690,7 +1470,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -1700,7 +1480,7 @@
                               <m:accPr>
                                 <m:chr m:val="̂"/>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1400" i="1">
+                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
@@ -1748,7 +1528,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="381000" y="9269730"/>
+              <a:off x="381000" y="22225000"/>
               <a:ext cx="180819" cy="231923"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1801,7 +1581,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
@@ -1855,9 +1635,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>104934</xdr:colOff>
+      <xdr:colOff>73184</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>197993</xdr:rowOff>
+      <xdr:rowOff>172593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="252762" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -1875,7 +1655,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1750854" y="197993"/>
+              <a:off x="1749584" y="172593"/>
               <a:ext cx="252762" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1906,15 +1686,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -1923,7 +1700,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -1969,7 +1746,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1750854" y="197993"/>
+              <a:off x="1749584" y="172593"/>
               <a:ext cx="252762" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2021,9 +1798,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>66834</xdr:colOff>
+      <xdr:colOff>117634</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>388493</xdr:rowOff>
+      <xdr:rowOff>382143</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180819" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -2041,7 +1818,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2550954" y="388493"/>
+              <a:off x="2644934" y="382143"/>
               <a:ext cx="180819" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2072,15 +1849,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2089,7 +1863,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -2135,7 +1909,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2550954" y="388493"/>
+              <a:off x="2644934" y="382143"/>
               <a:ext cx="180819" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2187,9 +1961,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>426720</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>110490</xdr:rowOff>
+      <xdr:colOff>210820</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>142240</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -2207,7 +1981,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3680460" y="5116830"/>
+              <a:off x="3519170" y="17331690"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2238,14 +2012,11 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2255,7 +2026,7 @@
                           <m:accPr>
                             <m:chr m:val="̅"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -2301,7 +2072,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3680460" y="5116830"/>
+              <a:off x="3519170" y="17331690"/>
               <a:ext cx="320040" cy="221214"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2347,9 +2118,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>525780</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>80010</xdr:rowOff>
+      <xdr:colOff>881380</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>67310</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180819" cy="251479"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
@@ -2367,7 +2138,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4549140" y="8964930"/>
+              <a:off x="4970780" y="21860510"/>
               <a:ext cx="180819" cy="251479"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2398,10 +2169,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̿"/>
@@ -2416,7 +2184,7 @@
                           <m:accPr>
                             <m:chr m:val="̂"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -2425,7 +2193,7 @@
                             <m:sSub>
                               <m:sSubPr>
                                 <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1400" i="1">
+                                  <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                     <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                   </a:rPr>
                                 </m:ctrlPr>
@@ -2473,7 +2241,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4549140" y="8964930"/>
+              <a:off x="4970780" y="21860510"/>
               <a:ext cx="180819" cy="251479"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2501,6 +2269,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1400" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -2525,7 +2294,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>318294</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>129413</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
@@ -2575,10 +2344,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2673,7 +2439,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>310674</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>83693</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="252762" cy="221214"/>
@@ -2723,15 +2489,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2740,7 +2503,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -2839,7 +2602,7 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>287814</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>83693</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180819" cy="221214"/>
@@ -2889,15 +2652,12 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:acc>
                       <m:accPr>
                         <m:chr m:val="̂"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2906,7 +2666,7 @@
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -3005,7 +2765,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>320040</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="320040" cy="221214"/>
@@ -3055,14 +2815,11 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -3072,7 +2829,7 @@
                           <m:accPr>
                             <m:chr m:val="̅"/>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1400" i="1">
+                              <a:rPr lang="en-US" sz="1400" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
@@ -3165,7 +2922,7 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>563880</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
@@ -3215,10 +2972,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -3307,6 +3061,171 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62F71959-41E3-484F-B4B2-DF492B39129A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="9217660"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6486A24E-FE7D-4F2C-ADFE-AEE90428B578}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="6855460"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="TextBox 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12DE7851-F42D-4D49-9151-5E44A8B06928}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5472430" y="7442200"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
@@ -3629,1021 +3548,2947 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABFF2E6-1E13-48EF-9BE3-D6C90C46BEC8}">
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:U212"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" customWidth="1"/>
-    <col min="14" max="14" width="9.6328125" customWidth="1"/>
+    <col min="4" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6328125" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.90625" customWidth="1"/>
+    <col min="17" max="17" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="46"/>
-    </row>
-    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+    <row r="1" spans="1:21" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="23"/>
+      <c r="U1"/>
+    </row>
+    <row r="2" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="U2"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10">
-        <v>1.24</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="11">
+        <v>3.49</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+      <c r="U3"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="11">
+        <v>3.2429999999999999</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8">
-        <v>0.48</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B5" s="11">
+        <v>3.52</v>
+      </c>
+      <c r="C5" s="12">
+        <f t="shared" ref="C5:C86" si="0">(0.5*B3+SUM(B4:B6)+0.5*B7)/4</f>
+        <v>3.7651249999999998</v>
+      </c>
+      <c r="D5" s="13">
+        <f>B5/C5</f>
+        <v>0.93489591979017961</v>
+      </c>
+      <c r="U5"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="11">
+        <v>3.6779999999999999</v>
+      </c>
+      <c r="C6" s="12">
+        <f t="shared" si="0"/>
+        <v>4.1869999999999994</v>
+      </c>
+      <c r="D6" s="13">
+        <f t="shared" ref="D6:D69" si="1">B6/C6</f>
+        <v>0.87843324576068793</v>
+      </c>
+      <c r="U6"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="11">
+        <v>5.7489999999999997</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="U7"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11">
+        <v>4.359</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="U8"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="14">
+        <v>4.37</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="U9"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="14">
+        <v>4.8369999999999997</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="U10"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="14">
+        <v>7.1230000000000002</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="U11"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="14">
+        <v>5.2859999999999996</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="U12"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="14">
+        <v>5.5629999999999997</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="U13"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="14">
+        <v>6.6059999999999999</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="U14"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="11">
+        <v>10.43</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="U15"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="11">
+        <v>7.98</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="U16"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="11">
+        <v>7.5609999999999999</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="U17"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="11">
+        <v>11.52</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="U18"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="11">
+        <v>11.88</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="U19"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="11">
+        <v>9.0839999999999996</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="U20"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="11">
+        <v>9.734</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="U21"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="11">
+        <v>12.207000000000001</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="U22"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="11">
+        <v>15.683</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="U23"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="11">
+        <v>13.499000000000001</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="U24"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="11">
+        <v>15.7</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="U25"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="11">
+        <v>20.343</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="U26"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="11">
+        <v>26.741</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="U27"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="11">
+        <v>24.667000000000002</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="U28"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="11">
+        <v>28.571000000000002</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="U29"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="11">
+        <v>28.27</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="U30"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="11">
+        <v>46.332999999999998</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="U31"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A32" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B32" s="11">
+        <v>39.186</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="U32"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="11">
+        <v>35.023000000000003</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="U33"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="11">
+        <v>35.966000000000001</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="U34"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="11">
+        <v>54.512</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="U35"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="11">
+        <v>43.603000000000002</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="U36"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="11">
+        <v>35.323</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="U37"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="11">
+        <v>37.472000000000001</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="U38"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="11">
+        <v>57.594000000000001</v>
+      </c>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="U39"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="11">
+        <v>45.646000000000001</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="U40"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A41" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="11">
+        <v>37.432000000000002</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="U41"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A42" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="11">
+        <v>42.122999999999998</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="U42"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A43" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="11">
+        <v>74.599000000000004</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="U43"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="11">
+        <v>58.01</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="U44"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A45" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="11">
+        <v>49.604999999999997</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="U45"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A46" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" s="11">
+        <v>51.500999999999998</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="U46"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A47" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" s="11">
+        <v>75.872</v>
+      </c>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="U47"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A48" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="11">
+        <v>50.557000000000002</v>
+      </c>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="U48"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A49" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B49" s="11">
+        <v>42.357999999999997</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="U49"/>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A50" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="11">
+        <v>46.851999999999997</v>
+      </c>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="U50"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A51" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="11">
+        <v>78.350999999999999</v>
+      </c>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="U51"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A52" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B52" s="11">
+        <v>52.896000000000001</v>
+      </c>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="U52"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A53" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="11">
+        <v>45.408000000000001</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="U53"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A54" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" s="11">
+        <v>52.579000000000001</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="U54"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A55" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="11">
+        <v>88.293000000000006</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="U55"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A56" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="11">
+        <v>61.137</v>
+      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="U56"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A57" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" s="11">
+        <v>53.265000000000001</v>
+      </c>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="U57"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A58" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="11">
+        <v>62.9</v>
+      </c>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="U58"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A59" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" s="11">
+        <v>84.31</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="U59"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A60" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60" s="11">
+        <v>58.015000000000001</v>
+      </c>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="U60"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A61" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61" s="11">
+        <v>53.808999999999997</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="U61"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A62" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B62" s="11">
+        <v>64.040000000000006</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="U62"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A63" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B63" s="11">
+        <v>91.819000000000003</v>
+      </c>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="U63"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A64" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64" s="11">
+        <v>58.313000000000002</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="U64"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A65" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="11">
+        <v>59.685000000000002</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="U65"/>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A66" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="11">
+        <v>64.697999999999993</v>
+      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="U66"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A67" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B67" s="11">
+        <v>111.43899999999999</v>
+      </c>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="U67"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A68" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B68" s="11">
+        <v>89.584000000000003</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="U68"/>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A69" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" s="11">
+        <v>81.433999999999997</v>
+      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="U69"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A70" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="11">
+        <v>83.36</v>
+      </c>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="U70"/>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A71" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B71" s="11">
+        <v>123.94499999999999</v>
+      </c>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="U71"/>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A72" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B72" s="11">
+        <v>97.278000000000006</v>
+      </c>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="U72"/>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A73" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73" s="11">
+        <v>82.959000000000003</v>
+      </c>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="U73"/>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A74" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B74" s="11">
+        <v>90.146000000000001</v>
+      </c>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="U74"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A75" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75" s="11">
+        <v>117.154</v>
+      </c>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="U75"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A76" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" s="11">
+        <v>94.835999999999999</v>
+      </c>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="U76"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A77" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B77" s="11">
+        <v>81.796999999999997</v>
+      </c>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="U77"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A78" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B78" s="11">
+        <v>89.498000000000005</v>
+      </c>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="U78"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A79" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B79" s="11">
+        <v>119.575</v>
+      </c>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="U79"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A80" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B80" s="11">
+        <v>90.753</v>
+      </c>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="U80"/>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A81" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B81" s="11">
+        <v>85.777000000000001</v>
+      </c>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="U81"/>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A82" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82" s="11">
+        <v>94.93</v>
+      </c>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="U82"/>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A83" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" s="11">
+        <v>124.3</v>
+      </c>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="U83"/>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A84" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" s="11">
+        <v>95.358999999999995</v>
+      </c>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="U84"/>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A85" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B85" s="11">
+        <v>94.036000000000001</v>
+      </c>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="U85"/>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A86" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B86" s="11">
+        <v>102.46599999999999</v>
+      </c>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="U86"/>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A87" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B87" s="11">
+        <v>143.756</v>
+      </c>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="U87"/>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A88" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B88" s="11">
+        <v>111.184</v>
+      </c>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="U88"/>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A89" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B89" s="11">
+        <v>109.417</v>
+      </c>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="U89"/>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B90" t="s">
+        <v>89</v>
+      </c>
+      <c r="U90"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B91" t="s">
+        <v>89</v>
+      </c>
+      <c r="U91"/>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A92" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B92" s="28"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="29"/>
+      <c r="U92"/>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A93" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="U93"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A94" s="15">
+        <v>2005</v>
+      </c>
+      <c r="B94" s="7" t="str" cm="1">
+        <f t="array" ref="B94:E94">TRANSPOSE(D3:D6)</f>
+        <v>NA</v>
+      </c>
+      <c r="C94" s="7" t="str">
+        <v>NA</v>
+      </c>
+      <c r="D94" s="6">
+        <v>0.93489591979017961</v>
+      </c>
+      <c r="E94" s="6">
+        <v>0.87843324576068793</v>
+      </c>
+      <c r="U94"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A95" s="15">
+        <v>2006</v>
+      </c>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="U95"/>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A96" s="15">
+        <v>2007</v>
+      </c>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="U96"/>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A97" s="15">
+        <v>2008</v>
+      </c>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="U97"/>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A98" s="15">
+        <v>2009</v>
+      </c>
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="U98"/>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A99" s="15">
+        <v>2010</v>
+      </c>
+      <c r="B99" s="7" t="str" cm="1">
+        <f t="array" ref="B99">IF(LEN(D23)&gt;0,TRANSPOSE(D23:D26),"")</f>
+        <v/>
+      </c>
+      <c r="C99" s="7"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="U99"/>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A100" s="15">
+        <v>2011</v>
+      </c>
+      <c r="B100" s="7" t="str" cm="1">
+        <f t="array" ref="B100">IF(LEN(D27)&gt;0,TRANSPOSE(D27:D30),"")</f>
+        <v/>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="U100"/>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A101" s="15">
+        <v>2012</v>
+      </c>
+      <c r="B101" s="7" t="str" cm="1">
+        <f t="array" ref="B101">IF(LEN(D31)&gt;0,TRANSPOSE(D31:D34),"")</f>
+        <v/>
+      </c>
+      <c r="C101" s="7"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="U101"/>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A102" s="15">
+        <v>2013</v>
+      </c>
+      <c r="B102" s="7" t="str" cm="1">
+        <f t="array" ref="B102">IF(LEN(D35)&gt;0,TRANSPOSE(D35:D38),"")</f>
+        <v/>
+      </c>
+      <c r="C102" s="7"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="U102"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A103" s="15">
+        <v>2014</v>
+      </c>
+      <c r="B103" s="7" t="str" cm="1">
+        <f t="array" ref="B103">IF(LEN(D39)&gt;0,TRANSPOSE(D39:D42),"")</f>
+        <v/>
+      </c>
+      <c r="C103" s="7"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="U103"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A104" s="15">
+        <v>2015</v>
+      </c>
+      <c r="B104" s="7" t="str" cm="1">
+        <f t="array" ref="B104">IF(LEN(D43)&gt;0,TRANSPOSE(D43:D46),"")</f>
+        <v/>
+      </c>
+      <c r="C104" s="7"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="U104"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A105" s="15">
+        <v>2016</v>
+      </c>
+      <c r="B105" s="7" t="str" cm="1">
+        <f t="array" ref="B105">IF(LEN(D47)&gt;0,TRANSPOSE(D47:D50),"")</f>
+        <v/>
+      </c>
+      <c r="C105" s="7"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="U105"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A106" s="15">
+        <v>2017</v>
+      </c>
+      <c r="B106" s="7" t="str" cm="1">
+        <f t="array" ref="B106">IF(LEN(D51)&gt;0,TRANSPOSE(D51:D54),"")</f>
+        <v/>
+      </c>
+      <c r="C106" s="7"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="U106"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A107" s="15">
+        <v>2018</v>
+      </c>
+      <c r="B107" s="7" t="str" cm="1">
+        <f t="array" ref="B107">IF(LEN(D55)&gt;0,TRANSPOSE(D55:D58),"")</f>
+        <v/>
+      </c>
+      <c r="C107" s="7"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="U107"/>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A108" s="15">
+        <v>2019</v>
+      </c>
+      <c r="B108" s="7" t="str" cm="1">
+        <f t="array" ref="B108">IF(LEN(D59)&gt;0,TRANSPOSE(D59:D62),"")</f>
+        <v/>
+      </c>
+      <c r="C108" s="7"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="U108"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A109" s="15">
+        <v>2020</v>
+      </c>
+      <c r="B109" s="7" t="str" cm="1">
+        <f t="array" ref="B109">IF(LEN(D63)&gt;0,TRANSPOSE(D63:D66),"")</f>
+        <v/>
+      </c>
+      <c r="C109" s="7"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="U109"/>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A110" s="15">
+        <v>2021</v>
+      </c>
+      <c r="B110" s="7" t="str" cm="1">
+        <f t="array" ref="B110">IF(LEN(D67)&gt;0,TRANSPOSE(D67:D70),"")</f>
+        <v/>
+      </c>
+      <c r="C110" s="7"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="U110"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A111" s="15">
+        <v>2022</v>
+      </c>
+      <c r="B111" s="7" t="str" cm="1">
+        <f t="array" ref="B111">IF(LEN(D71)&gt;0,TRANSPOSE(D71:D74),"")</f>
+        <v/>
+      </c>
+      <c r="C111" s="7"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="U111"/>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A112" s="15">
+        <v>2023</v>
+      </c>
+      <c r="B112" s="7" t="str" cm="1">
+        <f t="array" ref="B112">IF(LEN(D75)&gt;0,TRANSPOSE(D75:D78),"")</f>
+        <v/>
+      </c>
+      <c r="C112" s="7"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="U112"/>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A113" s="15">
+        <v>2024</v>
+      </c>
+      <c r="B113" s="7" t="str" cm="1">
+        <f t="array" ref="B113">IF(LEN(D79)&gt;0,TRANSPOSE(D79:D82),"")</f>
+        <v/>
+      </c>
+      <c r="C113" s="7"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="U113"/>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A114" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B114" s="7" t="str" cm="1">
+        <f t="array" ref="B114">IF(LEN(D83)&gt;0,TRANSPOSE(D83:D86),"")</f>
+        <v/>
+      </c>
+      <c r="C114" s="7"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
+      <c r="U114"/>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A115" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B115" s="7" t="str" cm="1">
+        <f t="array" ref="B115">IF(LEN(D87)&gt;0,TRANSPOSE(D87:D89),"")</f>
+        <v/>
+      </c>
+      <c r="C115" s="7"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="U115"/>
+    </row>
+    <row r="116" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="4"/>
+      <c r="B116" s="16"/>
+      <c r="C116" s="17"/>
+      <c r="D116" s="17"/>
+      <c r="E116" s="17"/>
+      <c r="F116" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="U116"/>
+    </row>
+    <row r="117" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B117" s="6">
+        <v>1.2842900914896718</v>
+      </c>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="U117"/>
+    </row>
+    <row r="118" spans="1:21" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="18"/>
+      <c r="B118" s="6">
+        <v>1.2863724151425917</v>
+      </c>
+      <c r="C118" s="5"/>
+      <c r="D118" s="5"/>
+      <c r="E118" s="5"/>
+      <c r="U118"/>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U119"/>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U120"/>
+    </row>
+    <row r="121" spans="1:21" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B121" s="25"/>
+      <c r="C121" s="25"/>
+      <c r="D121" s="25"/>
+      <c r="E121" s="25"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="26"/>
+      <c r="U121"/>
+    </row>
+    <row r="122" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+      <c r="A122" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="20"/>
+      <c r="F122" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="U122"/>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123" s="20" t="str">
+        <f t="shared" ref="A123:A154" si="2">A3</f>
+        <v>2005 Q1</v>
+      </c>
+      <c r="B123" s="20">
+        <f>IF(LEN(B3)&gt;0,B3,"")</f>
+        <v>3.49</v>
+      </c>
+      <c r="C123" s="7" t="str">
+        <f t="shared" ref="C123:D123" si="3">IF(LEN(C3)&gt;0,C3,"")</f>
+        <v>NA</v>
+      </c>
+      <c r="D123" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>NA</v>
+      </c>
+      <c r="E123" s="7">
+        <v>1.2863724151425917</v>
+      </c>
+      <c r="F123" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="G123" s="7">
+        <v>2.7130556897188605</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2005 Q2</v>
+      </c>
+      <c r="B124" s="20">
+        <f t="shared" ref="B124:D187" si="4">IF(LEN(B4)&gt;0,B4,"")</f>
+        <v>3.2429999999999999</v>
+      </c>
+      <c r="C124" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="D124" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>NA</v>
+      </c>
+      <c r="E124" s="5"/>
+      <c r="F124" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="8">
-        <v>1.24</v>
-      </c>
-      <c r="C5" s="52">
-        <v>1.3149999999999999</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="49">
-        <v>1.71</v>
-      </c>
-      <c r="C6" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="61" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="8">
-        <v>2.42</v>
-      </c>
-      <c r="C7" s="53">
-        <v>1.829</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="49">
-        <v>1.71</v>
-      </c>
-      <c r="C8" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="61" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="14">
-        <v>1.71</v>
-      </c>
-      <c r="C9" s="55">
-        <v>2.2509999999999999</v>
-      </c>
-      <c r="D9" s="62" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="50">
-        <v>2.19</v>
-      </c>
-      <c r="C10" s="62" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="54">
-        <v>0.80800000000000005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="14">
+      <c r="G124" s="7">
+        <v>3.4282183987311901</v>
+      </c>
+      <c r="M124" s="2"/>
+      <c r="U124"/>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2005 Q3</v>
+      </c>
+      <c r="B125" s="20">
+        <f t="shared" si="4"/>
+        <v>3.52</v>
+      </c>
+      <c r="C125" s="7">
+        <f t="shared" si="4"/>
+        <v>3.7651249999999998</v>
+      </c>
+      <c r="D125" s="7">
+        <f t="shared" si="4"/>
+        <v>0.93489591979017961</v>
+      </c>
+      <c r="E125" s="5"/>
+      <c r="F125" s="7">
+        <v>1.0984032752076216</v>
+      </c>
+      <c r="G125" s="7">
+        <v>4.1356256315660964</v>
+      </c>
+      <c r="M125" s="2"/>
+      <c r="U125"/>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2005 Q4</v>
+      </c>
+      <c r="B126" s="20">
+        <f t="shared" si="4"/>
+        <v>3.6779999999999999</v>
+      </c>
+      <c r="C126" s="7">
+        <f t="shared" si="4"/>
+        <v>4.1869999999999994</v>
+      </c>
+      <c r="D126" s="7">
+        <f t="shared" si="4"/>
+        <v>0.87843324576068793</v>
+      </c>
+      <c r="E126" s="5"/>
+      <c r="F126" s="6">
+        <v>0.95845011450849682</v>
+      </c>
+      <c r="G126" s="6">
+        <v>4.0130306294470754</v>
+      </c>
+      <c r="M126" s="2"/>
+      <c r="U126"/>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2006 Q1</v>
+      </c>
+      <c r="B127" s="20">
+        <f t="shared" si="4"/>
+        <v>5.7489999999999997</v>
+      </c>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="M127" s="2"/>
+      <c r="U127"/>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A128" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2006 Q2</v>
+      </c>
+      <c r="B128" s="20">
+        <f t="shared" si="4"/>
+        <v>4.359</v>
+      </c>
+      <c r="C128" s="5"/>
+      <c r="D128" s="5"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="M128" s="2"/>
+      <c r="U128"/>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A129" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2006 Q3</v>
+      </c>
+      <c r="B129" s="20">
+        <f t="shared" si="4"/>
         <v>4.37</v>
       </c>
-      <c r="C11" s="56">
-        <v>3.1360000000000001</v>
-      </c>
-      <c r="D11" s="15">
-        <v>1.393</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="14">
-        <v>3.42</v>
-      </c>
-      <c r="C12" s="14">
-        <v>3.4689999999999999</v>
-      </c>
-      <c r="D12" s="15">
-        <v>0.98599999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="14">
-        <v>3.42</v>
-      </c>
-      <c r="C13" s="14">
-        <v>3.956</v>
-      </c>
-      <c r="D13" s="15">
-        <v>0.86399999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="14">
-        <v>3.14</v>
-      </c>
-      <c r="C14" s="14">
-        <v>4.4740000000000002</v>
-      </c>
-      <c r="D14" s="15">
-        <v>0.70199999999999996</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="8">
-        <v>7.32</v>
-      </c>
-      <c r="C15" s="8">
-        <v>4.8010000000000002</v>
-      </c>
-      <c r="D15" s="13">
-        <v>1.5249999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="8">
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="C16" s="8">
-        <v>5.87</v>
-      </c>
-      <c r="D16" s="13">
-        <v>0.78500000000000003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="8">
+      <c r="C129" s="5"/>
+      <c r="D129" s="5"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="M129" s="2"/>
+      <c r="U129"/>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A130" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2006 Q4</v>
+      </c>
+      <c r="B130" s="20">
+        <f t="shared" si="4"/>
+        <v>4.8369999999999997</v>
+      </c>
+      <c r="C130" s="5"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="M130" s="2"/>
+      <c r="U130"/>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A131" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2007 Q1</v>
+      </c>
+      <c r="B131" s="20">
+        <f t="shared" si="4"/>
+        <v>7.1230000000000002</v>
+      </c>
+      <c r="C131" s="5"/>
+      <c r="D131" s="5"/>
+      <c r="E131" s="5"/>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="M131" s="2"/>
+      <c r="U131"/>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A132" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2007 Q2</v>
+      </c>
+      <c r="B132" s="20">
+        <f t="shared" si="4"/>
+        <v>5.2859999999999996</v>
+      </c>
+      <c r="C132" s="5"/>
+      <c r="D132" s="5"/>
+      <c r="E132" s="5"/>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="M132" s="2"/>
+      <c r="U132"/>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A133" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2007 Q3</v>
+      </c>
+      <c r="B133" s="20">
+        <f t="shared" si="4"/>
+        <v>5.5629999999999997</v>
+      </c>
+      <c r="C133" s="5"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="M133" s="2"/>
+      <c r="U133"/>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A134" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2007 Q4</v>
+      </c>
+      <c r="B134" s="20">
+        <f t="shared" si="4"/>
+        <v>6.6059999999999999</v>
+      </c>
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="M134" s="2"/>
+      <c r="U134"/>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A135" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2008 Q1</v>
+      </c>
+      <c r="B135" s="20">
+        <f t="shared" si="4"/>
+        <v>10.43</v>
+      </c>
+      <c r="C135" s="5"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="M135" s="2"/>
+      <c r="U135"/>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A136" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2008 Q2</v>
+      </c>
+      <c r="B136" s="20">
+        <f t="shared" si="4"/>
+        <v>7.98</v>
+      </c>
+      <c r="C136" s="5"/>
+      <c r="D136" s="5"/>
+      <c r="E136" s="5"/>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+      <c r="M136" s="2"/>
+      <c r="U136"/>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A137" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2008 Q3</v>
+      </c>
+      <c r="B137" s="20">
+        <f t="shared" si="4"/>
+        <v>7.5609999999999999</v>
+      </c>
+      <c r="C137" s="5"/>
+      <c r="D137" s="5"/>
+      <c r="E137" s="5"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="M137" s="2"/>
+      <c r="U137"/>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A138" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2008 Q4</v>
+      </c>
+      <c r="B138" s="20">
+        <f t="shared" si="4"/>
+        <v>11.52</v>
+      </c>
+      <c r="C138" s="5"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="5"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="M138" s="2"/>
+      <c r="U138"/>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A139" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2009 Q1</v>
+      </c>
+      <c r="B139" s="20">
+        <f t="shared" si="4"/>
+        <v>11.88</v>
+      </c>
+      <c r="C139" s="5"/>
+      <c r="D139" s="5"/>
+      <c r="E139" s="5"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="M139" s="2"/>
+      <c r="U139"/>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A140" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2009 Q2</v>
+      </c>
+      <c r="B140" s="20">
+        <f t="shared" si="4"/>
+        <v>9.0839999999999996</v>
+      </c>
+      <c r="C140" s="5"/>
+      <c r="D140" s="5"/>
+      <c r="E140" s="5"/>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="M140" s="2"/>
+      <c r="U140"/>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A141" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2009 Q3</v>
+      </c>
+      <c r="B141" s="20">
+        <f t="shared" si="4"/>
+        <v>9.734</v>
+      </c>
+      <c r="C141" s="5"/>
+      <c r="D141" s="5"/>
+      <c r="E141" s="5"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="M141" s="2"/>
+      <c r="U141"/>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A142" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2009 Q4</v>
+      </c>
+      <c r="B142" s="20">
+        <f t="shared" si="4"/>
+        <v>12.207000000000001</v>
+      </c>
+      <c r="C142" s="5"/>
+      <c r="D142" s="5"/>
+      <c r="E142" s="5"/>
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="M142" s="2"/>
+      <c r="U142"/>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A143" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2010 Q1</v>
+      </c>
+      <c r="B143" s="20">
+        <f t="shared" si="4"/>
+        <v>15.683</v>
+      </c>
+      <c r="C143" s="5"/>
+      <c r="D143" s="5"/>
+      <c r="E143" s="5"/>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="M143" s="2"/>
+      <c r="U143"/>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A144" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2010 Q2</v>
+      </c>
+      <c r="B144" s="20">
+        <f t="shared" si="4"/>
+        <v>13.499000000000001</v>
+      </c>
+      <c r="C144" s="5"/>
+      <c r="D144" s="5"/>
+      <c r="E144" s="5"/>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="M144" s="2"/>
+      <c r="U144"/>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A145" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2010 Q3</v>
+      </c>
+      <c r="B145" s="20">
+        <f t="shared" si="4"/>
+        <v>15.7</v>
+      </c>
+      <c r="C145" s="5"/>
+      <c r="D145" s="5"/>
+      <c r="E145" s="5"/>
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="M145" s="2"/>
+      <c r="U145"/>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A146" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2010 Q4</v>
+      </c>
+      <c r="B146" s="20">
+        <f t="shared" si="4"/>
+        <v>20.343</v>
+      </c>
+      <c r="C146" s="5"/>
+      <c r="D146" s="5"/>
+      <c r="E146" s="5"/>
+      <c r="F146" s="5"/>
+      <c r="G146" s="5"/>
+      <c r="M146" s="2"/>
+      <c r="U146"/>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A147" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2011 Q1</v>
+      </c>
+      <c r="B147" s="20">
+        <f t="shared" si="4"/>
+        <v>26.741</v>
+      </c>
+      <c r="C147" s="8"/>
+      <c r="D147" s="8"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="5"/>
+      <c r="G147" s="5"/>
+      <c r="M147" s="2"/>
+      <c r="U147"/>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A148" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2011 Q2</v>
+      </c>
+      <c r="B148" s="20">
+        <f t="shared" si="4"/>
+        <v>24.667000000000002</v>
+      </c>
+      <c r="C148" s="8"/>
+      <c r="D148" s="8"/>
+      <c r="E148" s="5"/>
+      <c r="F148" s="5"/>
+      <c r="G148" s="5"/>
+      <c r="M148" s="2"/>
+      <c r="U148"/>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A149" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2011 Q3</v>
+      </c>
+      <c r="B149" s="20">
+        <f t="shared" si="4"/>
+        <v>28.571000000000002</v>
+      </c>
+      <c r="C149" s="8"/>
+      <c r="D149" s="8"/>
+      <c r="E149" s="5"/>
+      <c r="F149" s="5"/>
+      <c r="G149" s="5"/>
+      <c r="M149" s="2"/>
+      <c r="U149"/>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A150" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2011 Q4</v>
+      </c>
+      <c r="B150" s="20">
+        <f t="shared" si="4"/>
+        <v>28.27</v>
+      </c>
+      <c r="C150" s="8"/>
+      <c r="D150" s="8"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="M150" s="2"/>
+      <c r="U150"/>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A151" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2012 Q1</v>
+      </c>
+      <c r="B151" s="20">
+        <f t="shared" si="4"/>
+        <v>46.332999999999998</v>
+      </c>
+      <c r="C151" s="8"/>
+      <c r="D151" s="8"/>
+      <c r="E151" s="5"/>
+      <c r="F151" s="5"/>
+      <c r="G151" s="5"/>
+      <c r="M151" s="2"/>
+      <c r="U151"/>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A152" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2012 Q2</v>
+      </c>
+      <c r="B152" s="20">
+        <f t="shared" si="4"/>
+        <v>39.186</v>
+      </c>
+      <c r="C152" s="8"/>
+      <c r="D152" s="8"/>
+      <c r="E152" s="5"/>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5"/>
+      <c r="M152" s="2"/>
+      <c r="U152"/>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A153" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2012 Q3</v>
+      </c>
+      <c r="B153" s="20">
+        <f t="shared" si="4"/>
+        <v>35.023000000000003</v>
+      </c>
+      <c r="C153" s="8"/>
+      <c r="D153" s="8"/>
+      <c r="E153" s="5"/>
+      <c r="F153" s="5"/>
+      <c r="G153" s="5"/>
+      <c r="M153" s="2"/>
+      <c r="U153"/>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A154" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>2012 Q4</v>
+      </c>
+      <c r="B154" s="20">
+        <f t="shared" si="4"/>
+        <v>35.966000000000001</v>
+      </c>
+      <c r="C154" s="8"/>
+      <c r="D154" s="8"/>
+      <c r="E154" s="5"/>
+      <c r="F154" s="5"/>
+      <c r="G154" s="5"/>
+      <c r="M154" s="2"/>
+      <c r="U154"/>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A155" s="20" t="str">
+        <f t="shared" ref="A155:A186" si="5">A35</f>
+        <v>2013 Q1</v>
+      </c>
+      <c r="B155" s="20">
+        <f t="shared" si="4"/>
+        <v>54.512</v>
+      </c>
+      <c r="C155" s="8"/>
+      <c r="D155" s="8"/>
+      <c r="E155" s="5"/>
+      <c r="F155" s="5"/>
+      <c r="G155" s="5"/>
+      <c r="M155" s="2"/>
+      <c r="U155"/>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A156" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2013 Q2</v>
+      </c>
+      <c r="B156" s="20">
+        <f t="shared" si="4"/>
+        <v>43.603000000000002</v>
+      </c>
+      <c r="C156" s="8"/>
+      <c r="D156" s="8"/>
+      <c r="E156" s="5"/>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5"/>
+      <c r="M156" s="2"/>
+      <c r="U156"/>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A157" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2013 Q3</v>
+      </c>
+      <c r="B157" s="20">
+        <f t="shared" si="4"/>
+        <v>35.323</v>
+      </c>
+      <c r="C157" s="8"/>
+      <c r="D157" s="8"/>
+      <c r="E157" s="5"/>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5"/>
+      <c r="M157" s="2"/>
+      <c r="U157"/>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A158" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2013 Q4</v>
+      </c>
+      <c r="B158" s="20">
+        <f t="shared" si="4"/>
+        <v>37.472000000000001</v>
+      </c>
+      <c r="C158" s="8"/>
+      <c r="D158" s="8"/>
+      <c r="E158" s="5"/>
+      <c r="F158" s="5"/>
+      <c r="G158" s="5"/>
+      <c r="M158" s="2"/>
+      <c r="U158"/>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A159" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2014 Q1</v>
+      </c>
+      <c r="B159" s="20">
+        <f t="shared" si="4"/>
+        <v>57.594000000000001</v>
+      </c>
+      <c r="C159" s="8"/>
+      <c r="D159" s="8"/>
+      <c r="E159" s="5"/>
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
+      <c r="M159" s="2"/>
+      <c r="U159"/>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A160" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2014 Q2</v>
+      </c>
+      <c r="B160" s="20">
+        <f t="shared" si="4"/>
+        <v>45.646000000000001</v>
+      </c>
+      <c r="C160" s="8"/>
+      <c r="D160" s="8"/>
+      <c r="E160" s="5"/>
+      <c r="F160" s="5"/>
+      <c r="G160" s="5"/>
+      <c r="M160" s="2"/>
+      <c r="U160"/>
+    </row>
+    <row r="161" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A161" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2014 Q3</v>
+      </c>
+      <c r="B161" s="20">
+        <f t="shared" si="4"/>
+        <v>37.432000000000002</v>
+      </c>
+      <c r="C161" s="8"/>
+      <c r="D161" s="8"/>
+      <c r="E161" s="5"/>
+      <c r="F161" s="5"/>
+      <c r="G161" s="5"/>
+      <c r="M161" s="2"/>
+      <c r="U161"/>
+    </row>
+    <row r="162" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A162" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2014 Q4</v>
+      </c>
+      <c r="B162" s="20">
+        <f t="shared" si="4"/>
+        <v>42.122999999999998</v>
+      </c>
+      <c r="C162" s="8"/>
+      <c r="D162" s="8"/>
+      <c r="E162" s="5"/>
+      <c r="F162" s="5"/>
+      <c r="G162" s="5"/>
+      <c r="M162" s="2"/>
+      <c r="U162"/>
+    </row>
+    <row r="163" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A163" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2015 Q1</v>
+      </c>
+      <c r="B163" s="20">
+        <f t="shared" si="4"/>
+        <v>74.599000000000004</v>
+      </c>
+      <c r="C163" s="8"/>
+      <c r="D163" s="8"/>
+      <c r="E163" s="5"/>
+      <c r="F163" s="5"/>
+      <c r="G163" s="5"/>
+      <c r="M163" s="2"/>
+      <c r="U163"/>
+    </row>
+    <row r="164" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A164" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2015 Q2</v>
+      </c>
+      <c r="B164" s="20">
+        <f t="shared" si="4"/>
+        <v>58.01</v>
+      </c>
+      <c r="C164" s="8"/>
+      <c r="D164" s="8"/>
+      <c r="E164" s="5"/>
+      <c r="F164" s="5"/>
+      <c r="G164" s="5"/>
+      <c r="M164" s="2"/>
+      <c r="U164"/>
+    </row>
+    <row r="165" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A165" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2015 Q3</v>
+      </c>
+      <c r="B165" s="20">
+        <f t="shared" si="4"/>
+        <v>49.604999999999997</v>
+      </c>
+      <c r="C165" s="8"/>
+      <c r="D165" s="8"/>
+      <c r="E165" s="5"/>
+      <c r="F165" s="5"/>
+      <c r="G165" s="5"/>
+      <c r="M165" s="2"/>
+      <c r="U165"/>
+    </row>
+    <row r="166" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A166" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2015 Q4</v>
+      </c>
+      <c r="B166" s="20">
+        <f t="shared" si="4"/>
+        <v>51.500999999999998</v>
+      </c>
+      <c r="C166" s="8"/>
+      <c r="D166" s="8"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5"/>
+      <c r="G166" s="5"/>
+      <c r="M166" s="2"/>
+      <c r="U166"/>
+    </row>
+    <row r="167" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A167" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2016 Q1</v>
+      </c>
+      <c r="B167" s="20">
+        <f t="shared" si="4"/>
+        <v>75.872</v>
+      </c>
+      <c r="C167" s="8"/>
+      <c r="D167" s="8"/>
+      <c r="E167" s="5"/>
+      <c r="F167" s="5"/>
+      <c r="G167" s="5"/>
+      <c r="M167" s="2"/>
+      <c r="U167"/>
+    </row>
+    <row r="168" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A168" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2016 Q2</v>
+      </c>
+      <c r="B168" s="20">
+        <f t="shared" si="4"/>
+        <v>50.557000000000002</v>
+      </c>
+      <c r="C168" s="8"/>
+      <c r="D168" s="8"/>
+      <c r="E168" s="5"/>
+      <c r="F168" s="5"/>
+      <c r="G168" s="5"/>
+      <c r="M168" s="2"/>
+      <c r="U168"/>
+    </row>
+    <row r="169" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A169" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2016 Q3</v>
+      </c>
+      <c r="B169" s="20">
+        <f t="shared" si="4"/>
+        <v>42.357999999999997</v>
+      </c>
+      <c r="C169" s="8"/>
+      <c r="D169" s="8"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
+      <c r="M169" s="2"/>
+      <c r="U169"/>
+    </row>
+    <row r="170" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A170" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2016 Q4</v>
+      </c>
+      <c r="B170" s="20">
+        <f t="shared" si="4"/>
+        <v>46.851999999999997</v>
+      </c>
+      <c r="C170" s="8"/>
+      <c r="D170" s="8"/>
+      <c r="E170" s="5"/>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5"/>
+      <c r="M170" s="2"/>
+      <c r="U170"/>
+    </row>
+    <row r="171" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A171" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2017 Q1</v>
+      </c>
+      <c r="B171" s="20">
+        <f t="shared" si="4"/>
+        <v>78.350999999999999</v>
+      </c>
+      <c r="C171" s="8"/>
+      <c r="D171" s="8"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5"/>
+      <c r="G171" s="5"/>
+      <c r="M171" s="2"/>
+      <c r="U171"/>
+    </row>
+    <row r="172" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A172" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2017 Q2</v>
+      </c>
+      <c r="B172" s="20">
+        <f t="shared" si="4"/>
+        <v>52.896000000000001</v>
+      </c>
+      <c r="C172" s="8"/>
+      <c r="D172" s="8"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="5"/>
+      <c r="G172" s="5"/>
+      <c r="M172" s="2"/>
+      <c r="U172"/>
+    </row>
+    <row r="173" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A173" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2017 Q3</v>
+      </c>
+      <c r="B173" s="20">
+        <f t="shared" si="4"/>
+        <v>45.408000000000001</v>
+      </c>
+      <c r="C173" s="8"/>
+      <c r="D173" s="8"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="5"/>
+      <c r="G173" s="5"/>
+      <c r="M173" s="2"/>
+      <c r="U173"/>
+    </row>
+    <row r="174" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A174" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2017 Q4</v>
+      </c>
+      <c r="B174" s="20">
+        <f t="shared" si="4"/>
+        <v>52.579000000000001</v>
+      </c>
+      <c r="C174" s="8"/>
+      <c r="D174" s="8"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5"/>
+      <c r="M174" s="2"/>
+      <c r="U174"/>
+    </row>
+    <row r="175" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A175" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2018 Q1</v>
+      </c>
+      <c r="B175" s="20">
+        <f t="shared" si="4"/>
+        <v>88.293000000000006</v>
+      </c>
+      <c r="C175" s="8"/>
+      <c r="D175" s="8"/>
+      <c r="E175" s="5"/>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5"/>
+      <c r="M175" s="2"/>
+      <c r="U175"/>
+    </row>
+    <row r="176" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A176" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2018 Q2</v>
+      </c>
+      <c r="B176" s="20">
+        <f t="shared" si="4"/>
+        <v>61.137</v>
+      </c>
+      <c r="C176" s="8"/>
+      <c r="D176" s="8"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="M176" s="2"/>
+      <c r="U176"/>
+    </row>
+    <row r="177" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A177" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2018 Q3</v>
+      </c>
+      <c r="B177" s="20">
+        <f t="shared" si="4"/>
+        <v>53.265000000000001</v>
+      </c>
+      <c r="C177" s="8"/>
+      <c r="D177" s="8"/>
+      <c r="E177" s="5"/>
+      <c r="F177" s="5"/>
+      <c r="G177" s="5"/>
+      <c r="M177" s="2"/>
+      <c r="U177"/>
+    </row>
+    <row r="178" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A178" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2018 Q4</v>
+      </c>
+      <c r="B178" s="20">
+        <f t="shared" si="4"/>
+        <v>62.9</v>
+      </c>
+      <c r="C178" s="8"/>
+      <c r="D178" s="8"/>
+      <c r="E178" s="5"/>
+      <c r="F178" s="5"/>
+      <c r="G178" s="5"/>
+      <c r="M178" s="2"/>
+      <c r="U178"/>
+    </row>
+    <row r="179" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A179" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2019 Q1</v>
+      </c>
+      <c r="B179" s="20">
+        <f t="shared" si="4"/>
+        <v>84.31</v>
+      </c>
+      <c r="C179" s="8"/>
+      <c r="D179" s="8"/>
+      <c r="E179" s="5"/>
+      <c r="F179" s="5"/>
+      <c r="G179" s="5"/>
+      <c r="M179" s="2"/>
+      <c r="U179"/>
+    </row>
+    <row r="180" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A180" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2019 Q2</v>
+      </c>
+      <c r="B180" s="20">
+        <f t="shared" si="4"/>
+        <v>58.015000000000001</v>
+      </c>
+      <c r="C180" s="8"/>
+      <c r="D180" s="8"/>
+      <c r="E180" s="5"/>
+      <c r="F180" s="5"/>
+      <c r="G180" s="5"/>
+      <c r="M180" s="2"/>
+      <c r="U180"/>
+    </row>
+    <row r="181" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A181" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2019 Q3</v>
+      </c>
+      <c r="B181" s="20">
+        <f t="shared" si="4"/>
+        <v>53.808999999999997</v>
+      </c>
+      <c r="C181" s="8"/>
+      <c r="D181" s="8"/>
+      <c r="E181" s="5"/>
+      <c r="F181" s="5"/>
+      <c r="G181" s="5"/>
+      <c r="M181" s="2"/>
+      <c r="U181"/>
+    </row>
+    <row r="182" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A182" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2019 Q4</v>
+      </c>
+      <c r="B182" s="20">
+        <f t="shared" si="4"/>
+        <v>64.040000000000006</v>
+      </c>
+      <c r="C182" s="8"/>
+      <c r="D182" s="8"/>
+      <c r="E182" s="5"/>
+      <c r="F182" s="5"/>
+      <c r="G182" s="5"/>
+      <c r="M182" s="2"/>
+      <c r="U182"/>
+    </row>
+    <row r="183" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A183" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2020 Q1</v>
+      </c>
+      <c r="B183" s="20">
+        <f t="shared" si="4"/>
+        <v>91.819000000000003</v>
+      </c>
+      <c r="C183" s="8"/>
+      <c r="D183" s="8"/>
+      <c r="E183" s="5"/>
+      <c r="F183" s="5"/>
+      <c r="G183" s="5"/>
+      <c r="M183" s="2"/>
+      <c r="U183"/>
+    </row>
+    <row r="184" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A184" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2020 Q2</v>
+      </c>
+      <c r="B184" s="20">
+        <f t="shared" si="4"/>
+        <v>58.313000000000002</v>
+      </c>
+      <c r="C184" s="8"/>
+      <c r="D184" s="8"/>
+      <c r="E184" s="5"/>
+      <c r="F184" s="5"/>
+      <c r="G184" s="5"/>
+      <c r="M184" s="2"/>
+      <c r="U184"/>
+    </row>
+    <row r="185" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A185" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2020 Q3</v>
+      </c>
+      <c r="B185" s="20">
+        <f t="shared" si="4"/>
+        <v>59.685000000000002</v>
+      </c>
+      <c r="C185" s="8"/>
+      <c r="D185" s="8"/>
+      <c r="E185" s="5"/>
+      <c r="F185" s="5"/>
+      <c r="G185" s="5"/>
+      <c r="M185" s="2"/>
+      <c r="U185"/>
+    </row>
+    <row r="186" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A186" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>2020 Q4</v>
+      </c>
+      <c r="B186" s="20">
+        <f t="shared" si="4"/>
+        <v>64.697999999999993</v>
+      </c>
+      <c r="C186" s="8"/>
+      <c r="D186" s="8"/>
+      <c r="E186" s="5"/>
+      <c r="F186" s="5"/>
+      <c r="G186" s="5"/>
+      <c r="M186" s="2"/>
+      <c r="U186"/>
+    </row>
+    <row r="187" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A187" s="20" t="str">
+        <f t="shared" ref="A187:A218" si="6">A67</f>
+        <v>2021 Q1</v>
+      </c>
+      <c r="B187" s="20">
+        <f t="shared" si="4"/>
+        <v>111.43899999999999</v>
+      </c>
+      <c r="C187" s="8"/>
+      <c r="D187" s="8"/>
+      <c r="E187" s="5"/>
+      <c r="F187" s="5"/>
+      <c r="G187" s="5"/>
+      <c r="M187" s="2"/>
+      <c r="U187"/>
+    </row>
+    <row r="188" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A188" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2021 Q2</v>
+      </c>
+      <c r="B188" s="20">
+        <f t="shared" ref="B188:D209" si="7">IF(LEN(B68)&gt;0,B68,"")</f>
+        <v>89.584000000000003</v>
+      </c>
+      <c r="C188" s="8"/>
+      <c r="D188" s="8"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="5"/>
+      <c r="G188" s="5"/>
+      <c r="M188" s="2"/>
+      <c r="U188"/>
+    </row>
+    <row r="189" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A189" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2021 Q3</v>
+      </c>
+      <c r="B189" s="20">
+        <f t="shared" si="7"/>
+        <v>81.433999999999997</v>
+      </c>
+      <c r="C189" s="8"/>
+      <c r="D189" s="8"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="5"/>
+      <c r="G189" s="5"/>
+      <c r="M189" s="2"/>
+      <c r="U189"/>
+    </row>
+    <row r="190" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A190" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2021 Q4</v>
+      </c>
+      <c r="B190" s="20">
+        <f t="shared" si="7"/>
+        <v>83.36</v>
+      </c>
+      <c r="C190" s="8"/>
+      <c r="D190" s="8"/>
+      <c r="E190" s="5"/>
+      <c r="F190" s="5"/>
+      <c r="G190" s="5"/>
+      <c r="M190" s="2"/>
+      <c r="U190"/>
+    </row>
+    <row r="191" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A191" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2022 Q1</v>
+      </c>
+      <c r="B191" s="20">
+        <f t="shared" si="7"/>
+        <v>123.94499999999999</v>
+      </c>
+      <c r="C191" s="8"/>
+      <c r="D191" s="8"/>
+      <c r="E191" s="5"/>
+      <c r="F191" s="5"/>
+      <c r="G191" s="5"/>
+      <c r="M191" s="2"/>
+      <c r="U191"/>
+    </row>
+    <row r="192" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A192" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2022 Q2</v>
+      </c>
+      <c r="B192" s="20">
+        <f t="shared" si="7"/>
+        <v>97.278000000000006</v>
+      </c>
+      <c r="C192" s="8"/>
+      <c r="D192" s="8"/>
+      <c r="E192" s="5"/>
+      <c r="F192" s="5"/>
+      <c r="G192" s="5"/>
+      <c r="M192" s="2"/>
+      <c r="U192"/>
+    </row>
+    <row r="193" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A193" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2022 Q3</v>
+      </c>
+      <c r="B193" s="20">
+        <f t="shared" si="7"/>
+        <v>82.959000000000003</v>
+      </c>
+      <c r="C193" s="8"/>
+      <c r="D193" s="8"/>
+      <c r="E193" s="5"/>
+      <c r="F193" s="5"/>
+      <c r="G193" s="5"/>
+      <c r="M193" s="2"/>
+      <c r="U193"/>
+    </row>
+    <row r="194" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A194" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2022 Q4</v>
+      </c>
+      <c r="B194" s="20">
+        <f t="shared" si="7"/>
         <v>90.146000000000001</v>
       </c>
-      <c r="C18" s="8">
-        <v>96.578999999999994</v>
-      </c>
-      <c r="D18" s="13">
-        <v>0.93300000000000005</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="8">
+      <c r="C194" s="8"/>
+      <c r="D194" s="8"/>
+      <c r="E194" s="5"/>
+      <c r="F194" s="5"/>
+      <c r="G194" s="5"/>
+      <c r="M194" s="2"/>
+      <c r="U194"/>
+    </row>
+    <row r="195" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A195" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2023 Q1</v>
+      </c>
+      <c r="B195" s="20">
+        <f t="shared" si="7"/>
         <v>117.154</v>
       </c>
-      <c r="C19" s="8">
-        <v>96.128</v>
-      </c>
-      <c r="D19" s="13">
-        <v>1.2190000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="C195" s="8"/>
+      <c r="D195" s="8"/>
+      <c r="E195" s="5"/>
+      <c r="F195" s="5"/>
+      <c r="G195" s="5"/>
+      <c r="M195" s="2"/>
+      <c r="U195"/>
+    </row>
+    <row r="196" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A196" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2023 Q2</v>
+      </c>
+      <c r="B196" s="20">
+        <f t="shared" si="7"/>
         <v>94.835999999999999</v>
       </c>
-      <c r="C20" s="8">
-        <v>95.902000000000001</v>
-      </c>
-      <c r="D20" s="13">
-        <v>0.98899999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="8">
+      <c r="C196" s="8"/>
+      <c r="D196" s="8"/>
+      <c r="E196" s="5"/>
+      <c r="F196" s="5"/>
+      <c r="G196" s="5"/>
+      <c r="M196" s="2"/>
+      <c r="U196"/>
+    </row>
+    <row r="197" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A197" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2023 Q3</v>
+      </c>
+      <c r="B197" s="20">
+        <f t="shared" si="7"/>
         <v>81.796999999999997</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="26">
+      <c r="C197" s="8"/>
+      <c r="D197" s="8"/>
+      <c r="E197" s="5"/>
+      <c r="F197" s="5"/>
+      <c r="G197" s="5"/>
+      <c r="M197" s="2"/>
+      <c r="U197"/>
+    </row>
+    <row r="198" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A198" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2023 Q4</v>
+      </c>
+      <c r="B198" s="20">
+        <f t="shared" si="7"/>
         <v>89.498000000000005</v>
       </c>
-      <c r="C22" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="7">
-        <v>2005</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" s="60" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="7">
-        <v>2006</v>
-      </c>
-      <c r="B28" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="20">
-        <v>0.80800000000000005</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="7">
-        <v>2007</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1.393</v>
-      </c>
-      <c r="C29" s="1">
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E29" s="20">
-        <v>0.70199999999999996</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="7">
-        <v>2008</v>
-      </c>
-      <c r="B30" s="1">
-        <v>1.5249999999999999</v>
-      </c>
-      <c r="C30" s="1">
-        <v>0.78500000000000003</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0.68300000000000005</v>
-      </c>
-      <c r="E30" s="20">
-        <v>1.325</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="7">
-        <v>2009</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1.1819999999999999</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0.83399999999999996</v>
-      </c>
-      <c r="E31" s="20">
-        <v>1.0049999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="7">
-        <v>2010</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1.1930000000000001</v>
-      </c>
-      <c r="C32" s="1">
-        <v>0.91200000000000003</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0.84899999999999998</v>
-      </c>
-      <c r="E32" s="20">
-        <v>0.96299999999999997</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="19.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="7">
-        <v>2011</v>
-      </c>
-      <c r="B33" s="1">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="C33" s="1">
-        <v>0.96099999999999997</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0.999</v>
-      </c>
-      <c r="E33" s="1">
-        <v>0.73399999999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="7">
-        <v>2012</v>
-      </c>
-      <c r="B34">
-        <v>1.3280000000000001</v>
-      </c>
-      <c r="C34">
-        <v>1.141</v>
-      </c>
-      <c r="D34">
-        <v>0.86499999999999999</v>
-      </c>
-      <c r="E34" s="19">
-        <v>0.82799999999999996</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="7">
-        <v>2013</v>
-      </c>
-      <c r="B35">
-        <v>1.2490000000000001</v>
-      </c>
-      <c r="C35">
-        <v>1.0189999999999999</v>
-      </c>
-      <c r="D35">
-        <v>0.81899999999999995</v>
-      </c>
-      <c r="E35" s="19">
-        <v>0.85599999999999998</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="7">
-        <v>2014</v>
-      </c>
-      <c r="B36">
-        <v>1.3009999999999999</v>
-      </c>
-      <c r="C36">
-        <v>1.012</v>
-      </c>
-      <c r="D36">
-        <v>0.78300000000000003</v>
-      </c>
-      <c r="E36" s="19">
-        <v>0.81799999999999995</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="7">
-        <v>2015</v>
-      </c>
-      <c r="B37">
-        <v>1.367</v>
-      </c>
-      <c r="C37">
-        <v>1.0129999999999999</v>
-      </c>
-      <c r="D37">
-        <v>0.84699999999999998</v>
-      </c>
-      <c r="E37" s="19">
-        <v>0.89100000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="7">
-        <v>2016</v>
-      </c>
-      <c r="B38">
-        <v>1.355</v>
-      </c>
-      <c r="C38">
-        <v>0.92800000000000005</v>
-      </c>
-      <c r="D38">
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="E38" s="19">
-        <v>0.85499999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="7">
-        <v>2017</v>
-      </c>
-      <c r="B39">
-        <v>1.4119999999999999</v>
-      </c>
-      <c r="C39">
-        <v>0.93500000000000005</v>
-      </c>
-      <c r="D39">
-        <v>0.77600000000000002</v>
-      </c>
-      <c r="E39" s="19">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="7">
-        <v>2018</v>
-      </c>
-      <c r="B40" s="1">
-        <v>1.405</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0.93899999999999995</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0.80800000000000005</v>
-      </c>
-      <c r="E40" s="20">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="7">
-        <v>2019</v>
-      </c>
-      <c r="B41" s="1">
-        <v>1.3029999999999999</v>
-      </c>
-      <c r="C41" s="1">
-        <v>0.89400000000000002</v>
-      </c>
-      <c r="D41" s="1">
-        <v>0.81599999999999995</v>
-      </c>
-      <c r="E41" s="20">
-        <v>0.95599999999999996</v>
-      </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="7">
-        <v>2020</v>
-      </c>
-      <c r="B42" s="1">
-        <v>1.3560000000000001</v>
-      </c>
-      <c r="C42" s="1">
-        <v>0.85099999999999998</v>
-      </c>
-      <c r="D42" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="E42" s="20">
-        <v>0.83499999999999996</v>
-      </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="7">
-        <v>2021</v>
-      </c>
-      <c r="B43" s="1">
-        <v>1.3260000000000001</v>
-      </c>
-      <c r="C43" s="1">
-        <v>1.0049999999999999</v>
-      </c>
-      <c r="D43" s="1">
-        <v>0.875</v>
-      </c>
-      <c r="E43" s="20">
-        <v>0.872</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="7">
-        <v>2022</v>
-      </c>
-      <c r="B44" s="1">
-        <v>1.282</v>
-      </c>
-      <c r="C44" s="1">
-        <v>0.995</v>
-      </c>
-      <c r="D44" s="1">
-        <v>0.84899999999999998</v>
-      </c>
-      <c r="E44" s="20">
-        <v>0.93300000000000005</v>
-      </c>
-      <c r="F44" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="7">
-        <v>2023</v>
-      </c>
-      <c r="B45" s="1">
-        <v>1.2190000000000001</v>
-      </c>
-      <c r="C45" s="1">
-        <v>0.98899999999999999</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F45" s="48"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-    </row>
-    <row r="46" spans="1:14" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="B46" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="C46" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E46" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="58"/>
-    </row>
-    <row r="47" spans="1:14" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="21"/>
-      <c r="B47" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="C47" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" s="57" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A52" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="B52" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="G52" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" s="34">
-        <v>1.24</v>
-      </c>
-      <c r="C53" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="E53" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="F53" s="35" t="s">
-        <v>2</v>
-      </c>
-      <c r="G53" s="36" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B54">
-        <v>0.48</v>
-      </c>
-      <c r="C54" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="E54" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="F54" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="G54" s="39" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55">
-        <v>1.24</v>
-      </c>
-      <c r="C55">
-        <v>1.3149999999999999</v>
-      </c>
-      <c r="D55" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E55" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="G55" s="57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56">
-        <v>1.71</v>
-      </c>
-      <c r="C56">
-        <v>1.6160000000000001</v>
-      </c>
-      <c r="D56" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E56" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="F56" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="G56" s="57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="B57">
-        <v>2.42</v>
-      </c>
-      <c r="C57">
-        <v>1.829</v>
-      </c>
-      <c r="D57" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E57" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58">
-        <v>1.71</v>
-      </c>
-      <c r="C58">
-        <v>1.9470000000000001</v>
-      </c>
-      <c r="D58" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E58" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59">
-        <v>1.71</v>
-      </c>
-      <c r="C59">
-        <v>2.2509999999999999</v>
-      </c>
-      <c r="D59" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60">
-        <v>2.19</v>
-      </c>
-      <c r="C60">
-        <v>2.7090000000000001</v>
-      </c>
-      <c r="D60">
-        <v>0.80800000000000005</v>
-      </c>
-      <c r="E60">
-        <v>0.90500000000000003</v>
-      </c>
-      <c r="F60">
-        <v>0.89300000000000002</v>
-      </c>
-      <c r="G60" s="40">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="B61">
-        <v>4.37</v>
-      </c>
-      <c r="C61">
-        <v>3.1360000000000001</v>
-      </c>
-      <c r="D61">
-        <v>1.393</v>
-      </c>
-      <c r="E61">
-        <v>1.3140000000000001</v>
-      </c>
-      <c r="F61">
-        <v>1.06</v>
-      </c>
-      <c r="G61" s="40">
-        <v>3.3250000000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B62">
-        <v>3.42</v>
-      </c>
-      <c r="C62">
-        <v>3.4689999999999999</v>
-      </c>
-      <c r="D62">
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="E62">
-        <v>0.94699999999999995</v>
-      </c>
-      <c r="F62">
-        <v>1.0409999999999999</v>
-      </c>
-      <c r="G62" s="40">
-        <v>3.6120000000000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="B63" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="G63" s="43" t="s">
-        <v>18</v>
-      </c>
+      <c r="C198" s="8"/>
+      <c r="D198" s="8"/>
+      <c r="E198" s="5"/>
+      <c r="F198" s="5"/>
+      <c r="G198" s="5"/>
+      <c r="M198" s="2"/>
+      <c r="U198"/>
+    </row>
+    <row r="199" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A199" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2024 Q1</v>
+      </c>
+      <c r="B199" s="20">
+        <f t="shared" si="7"/>
+        <v>119.575</v>
+      </c>
+      <c r="C199" s="8"/>
+      <c r="D199" s="8"/>
+      <c r="E199" s="5"/>
+      <c r="F199" s="5"/>
+      <c r="G199" s="5"/>
+      <c r="M199" s="2"/>
+      <c r="U199"/>
+    </row>
+    <row r="200" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A200" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2024 Q2</v>
+      </c>
+      <c r="B200" s="20">
+        <f t="shared" si="7"/>
+        <v>90.753</v>
+      </c>
+      <c r="C200" s="8"/>
+      <c r="D200" s="8"/>
+      <c r="E200" s="5"/>
+      <c r="F200" s="5"/>
+      <c r="G200" s="5"/>
+      <c r="M200" s="2"/>
+      <c r="U200"/>
+    </row>
+    <row r="201" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A201" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2024 Q3</v>
+      </c>
+      <c r="B201" s="20">
+        <f t="shared" si="7"/>
+        <v>85.777000000000001</v>
+      </c>
+      <c r="C201" s="8"/>
+      <c r="D201" s="8"/>
+      <c r="E201" s="5"/>
+      <c r="F201" s="5"/>
+      <c r="G201" s="5"/>
+      <c r="M201" s="2"/>
+      <c r="U201"/>
+    </row>
+    <row r="202" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A202" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2024 Q4</v>
+      </c>
+      <c r="B202" s="20">
+        <f t="shared" si="7"/>
+        <v>94.93</v>
+      </c>
+      <c r="C202" s="8"/>
+      <c r="D202" s="8"/>
+      <c r="E202" s="5"/>
+      <c r="F202" s="5"/>
+      <c r="G202" s="5"/>
+      <c r="M202" s="2"/>
+      <c r="U202"/>
+    </row>
+    <row r="203" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A203" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2025 Q1</v>
+      </c>
+      <c r="B203" s="20">
+        <f t="shared" si="7"/>
+        <v>124.3</v>
+      </c>
+      <c r="C203" s="8"/>
+      <c r="D203" s="8"/>
+      <c r="E203" s="5"/>
+      <c r="F203" s="5"/>
+      <c r="G203" s="5"/>
+      <c r="M203" s="2"/>
+      <c r="U203"/>
+    </row>
+    <row r="204" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A204" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2025 Q2</v>
+      </c>
+      <c r="B204" s="20">
+        <f t="shared" si="7"/>
+        <v>95.358999999999995</v>
+      </c>
+      <c r="C204" s="8"/>
+      <c r="D204" s="8"/>
+      <c r="E204" s="5"/>
+      <c r="F204" s="5"/>
+      <c r="G204" s="5"/>
+      <c r="M204" s="2"/>
+      <c r="U204"/>
+    </row>
+    <row r="205" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A205" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2025 Q3</v>
+      </c>
+      <c r="B205" s="20">
+        <f t="shared" si="7"/>
+        <v>94.036000000000001</v>
+      </c>
+      <c r="C205" s="8"/>
+      <c r="D205" s="8"/>
+      <c r="E205" s="5"/>
+      <c r="F205" s="5"/>
+      <c r="G205" s="5"/>
+      <c r="M205" s="2"/>
+      <c r="U205"/>
+    </row>
+    <row r="206" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A206" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2025 Q4</v>
+      </c>
+      <c r="B206" s="20">
+        <f t="shared" si="7"/>
+        <v>102.46599999999999</v>
+      </c>
+      <c r="C206" s="8"/>
+      <c r="D206" s="8"/>
+      <c r="E206" s="5"/>
+      <c r="F206" s="5"/>
+      <c r="G206" s="5"/>
+      <c r="M206" s="2"/>
+      <c r="U206"/>
+    </row>
+    <row r="207" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A207" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2026 Q1</v>
+      </c>
+      <c r="B207" s="20">
+        <f t="shared" si="7"/>
+        <v>143.756</v>
+      </c>
+      <c r="C207" s="8"/>
+      <c r="D207" s="8"/>
+      <c r="E207" s="5"/>
+      <c r="F207" s="5"/>
+      <c r="G207" s="5"/>
+      <c r="M207" s="2"/>
+      <c r="U207"/>
+    </row>
+    <row r="208" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A208" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2026 Q2</v>
+      </c>
+      <c r="B208" s="20">
+        <f t="shared" si="7"/>
+        <v>111.184</v>
+      </c>
+      <c r="C208" s="8"/>
+      <c r="D208" s="8"/>
+      <c r="E208" s="5"/>
+      <c r="F208" s="5"/>
+      <c r="G208" s="5"/>
+      <c r="M208" s="2"/>
+      <c r="U208"/>
+    </row>
+    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A209" s="20" t="str">
+        <f t="shared" si="6"/>
+        <v>2026 Q3</v>
+      </c>
+      <c r="B209" s="20">
+        <f t="shared" si="7"/>
+        <v>109.417</v>
+      </c>
+      <c r="C209" s="8"/>
+      <c r="D209" s="8"/>
+      <c r="E209" s="5"/>
+      <c r="F209" s="5"/>
+      <c r="G209" s="5"/>
+      <c r="M209" s="2"/>
+      <c r="U209"/>
+    </row>
+    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M210" s="2"/>
+      <c r="U210"/>
+    </row>
+    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M211" s="2"/>
+      <c r="U211"/>
+    </row>
+    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="M212" s="2"/>
+      <c r="U212"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="A121:G121"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4652,15 +6497,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -4855,7 +6691,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
@@ -4863,15 +6699,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4890,7 +6727,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4905,4 +6742,12 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/handouts/chapter_1_5_handout.xlsx
+++ b/docs/handouts/chapter_1_5_handout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56789BC9-1F85-4027-B672-BC14645CC5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D827B22-62B8-48ED-81D3-A13987247CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -151,224 +151,224 @@
     <t xml:space="preserve">Seasonally Adjusted </t>
   </si>
   <si>
-    <t>Table 1: Computation of the 
+    <t>2008 Q3</t>
+  </si>
+  <si>
+    <t>2008 Q4</t>
+  </si>
+  <si>
+    <t>2009 Q1</t>
+  </si>
+  <si>
+    <t>2009 Q2</t>
+  </si>
+  <si>
+    <t>2009 Q3</t>
+  </si>
+  <si>
+    <t>2009 Q4</t>
+  </si>
+  <si>
+    <t>2010 Q1</t>
+  </si>
+  <si>
+    <t>2010 Q2</t>
+  </si>
+  <si>
+    <t>2010 Q3</t>
+  </si>
+  <si>
+    <t>2010 Q4</t>
+  </si>
+  <si>
+    <t>2011 Q1</t>
+  </si>
+  <si>
+    <t>2011 Q2</t>
+  </si>
+  <si>
+    <t>2011 Q3</t>
+  </si>
+  <si>
+    <t>2011 Q4</t>
+  </si>
+  <si>
+    <t>2012 Q1</t>
+  </si>
+  <si>
+    <t>2012 Q2</t>
+  </si>
+  <si>
+    <t>2012 Q3</t>
+  </si>
+  <si>
+    <t>2012 Q4</t>
+  </si>
+  <si>
+    <t>2013 Q1</t>
+  </si>
+  <si>
+    <t>2013 Q2</t>
+  </si>
+  <si>
+    <t>2013 Q3</t>
+  </si>
+  <si>
+    <t>2013 Q4</t>
+  </si>
+  <si>
+    <t>2014 Q1</t>
+  </si>
+  <si>
+    <t>2014 Q2</t>
+  </si>
+  <si>
+    <t>2014 Q3</t>
+  </si>
+  <si>
+    <t>2014 Q4</t>
+  </si>
+  <si>
+    <t>2015 Q1</t>
+  </si>
+  <si>
+    <t>2015 Q2</t>
+  </si>
+  <si>
+    <t>2015 Q3</t>
+  </si>
+  <si>
+    <t>2015 Q4</t>
+  </si>
+  <si>
+    <t>2016 Q1</t>
+  </si>
+  <si>
+    <t>2016 Q2</t>
+  </si>
+  <si>
+    <t>2016 Q3</t>
+  </si>
+  <si>
+    <t>2016 Q4</t>
+  </si>
+  <si>
+    <t>2017 Q1</t>
+  </si>
+  <si>
+    <t>2017 Q2</t>
+  </si>
+  <si>
+    <t>2017 Q3</t>
+  </si>
+  <si>
+    <t>2017 Q4</t>
+  </si>
+  <si>
+    <t>2018 Q1</t>
+  </si>
+  <si>
+    <t>2018 Q2</t>
+  </si>
+  <si>
+    <t>2018 Q3</t>
+  </si>
+  <si>
+    <t>2018 Q4</t>
+  </si>
+  <si>
+    <t>2019 Q1</t>
+  </si>
+  <si>
+    <t>2019 Q2</t>
+  </si>
+  <si>
+    <t>2019 Q3</t>
+  </si>
+  <si>
+    <t>2019 Q4</t>
+  </si>
+  <si>
+    <t>2020 Q1</t>
+  </si>
+  <si>
+    <t>2020 Q2</t>
+  </si>
+  <si>
+    <t>2020 Q3</t>
+  </si>
+  <si>
+    <t>2020 Q4</t>
+  </si>
+  <si>
+    <t>2021 Q1</t>
+  </si>
+  <si>
+    <t>2021 Q2</t>
+  </si>
+  <si>
+    <t>2021 Q3</t>
+  </si>
+  <si>
+    <t>2021 Q4</t>
+  </si>
+  <si>
+    <t>2022 Q1</t>
+  </si>
+  <si>
+    <t>2022 Q2</t>
+  </si>
+  <si>
+    <t>2022 Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>2024 Q1</t>
+  </si>
+  <si>
+    <t>2024 Q2</t>
+  </si>
+  <si>
+    <t>2024 Q3</t>
+  </si>
+  <si>
+    <t>2024 Q4</t>
+  </si>
+  <si>
+    <t>2025 Q1</t>
+  </si>
+  <si>
+    <t>2025 Q2</t>
+  </si>
+  <si>
+    <t>2025 Q3</t>
+  </si>
+  <si>
+    <t>2025 Q4</t>
+  </si>
+  <si>
+    <t>2026 Q1</t>
+  </si>
+  <si>
+    <t>2026 Q2</t>
+  </si>
+  <si>
+    <t>2026 Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Mean, </t>
+  </si>
+  <si>
+    <t>Table 3: Computation of the 
 Centered Moving Average,             , and the Estimated Quarterly Multiplicative Effect,</t>
   </si>
   <si>
-    <t>Table 2: Computation of Seasonally Adjusted Factors,</t>
-  </si>
-  <si>
-    <t>2008 Q3</t>
-  </si>
-  <si>
-    <t>2008 Q4</t>
-  </si>
-  <si>
-    <t>2009 Q1</t>
-  </si>
-  <si>
-    <t>2009 Q2</t>
-  </si>
-  <si>
-    <t>2009 Q3</t>
-  </si>
-  <si>
-    <t>2009 Q4</t>
-  </si>
-  <si>
-    <t>2010 Q1</t>
-  </si>
-  <si>
-    <t>2010 Q2</t>
-  </si>
-  <si>
-    <t>2010 Q3</t>
-  </si>
-  <si>
-    <t>2010 Q4</t>
-  </si>
-  <si>
-    <t>2011 Q1</t>
-  </si>
-  <si>
-    <t>2011 Q2</t>
-  </si>
-  <si>
-    <t>2011 Q3</t>
-  </si>
-  <si>
-    <t>2011 Q4</t>
-  </si>
-  <si>
-    <t>2012 Q1</t>
-  </si>
-  <si>
-    <t>2012 Q2</t>
-  </si>
-  <si>
-    <t>2012 Q3</t>
-  </si>
-  <si>
-    <t>2012 Q4</t>
-  </si>
-  <si>
-    <t>2013 Q1</t>
-  </si>
-  <si>
-    <t>2013 Q2</t>
-  </si>
-  <si>
-    <t>2013 Q3</t>
-  </si>
-  <si>
-    <t>2013 Q4</t>
-  </si>
-  <si>
-    <t>2014 Q1</t>
-  </si>
-  <si>
-    <t>2014 Q2</t>
-  </si>
-  <si>
-    <t>2014 Q3</t>
-  </si>
-  <si>
-    <t>2014 Q4</t>
-  </si>
-  <si>
-    <t>2015 Q1</t>
-  </si>
-  <si>
-    <t>2015 Q2</t>
-  </si>
-  <si>
-    <t>2015 Q3</t>
-  </si>
-  <si>
-    <t>2015 Q4</t>
-  </si>
-  <si>
-    <t>2016 Q1</t>
-  </si>
-  <si>
-    <t>2016 Q2</t>
-  </si>
-  <si>
-    <t>2016 Q3</t>
-  </si>
-  <si>
-    <t>2016 Q4</t>
-  </si>
-  <si>
-    <t>2017 Q1</t>
-  </si>
-  <si>
-    <t>2017 Q2</t>
-  </si>
-  <si>
-    <t>2017 Q3</t>
-  </si>
-  <si>
-    <t>2017 Q4</t>
-  </si>
-  <si>
-    <t>2018 Q1</t>
-  </si>
-  <si>
-    <t>2018 Q2</t>
-  </si>
-  <si>
-    <t>2018 Q3</t>
-  </si>
-  <si>
-    <t>2018 Q4</t>
-  </si>
-  <si>
-    <t>2019 Q1</t>
-  </si>
-  <si>
-    <t>2019 Q2</t>
-  </si>
-  <si>
-    <t>2019 Q3</t>
-  </si>
-  <si>
-    <t>2019 Q4</t>
-  </si>
-  <si>
-    <t>2020 Q1</t>
-  </si>
-  <si>
-    <t>2020 Q2</t>
-  </si>
-  <si>
-    <t>2020 Q3</t>
-  </si>
-  <si>
-    <t>2020 Q4</t>
-  </si>
-  <si>
-    <t>2021 Q1</t>
-  </si>
-  <si>
-    <t>2021 Q2</t>
-  </si>
-  <si>
-    <t>2021 Q3</t>
-  </si>
-  <si>
-    <t>2021 Q4</t>
-  </si>
-  <si>
-    <t>2022 Q1</t>
-  </si>
-  <si>
-    <t>2022 Q2</t>
-  </si>
-  <si>
-    <t>2022 Q3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>2024 Q1</t>
-  </si>
-  <si>
-    <t>2024 Q2</t>
-  </si>
-  <si>
-    <t>2024 Q3</t>
-  </si>
-  <si>
-    <t>2024 Q4</t>
-  </si>
-  <si>
-    <t>2025 Q1</t>
-  </si>
-  <si>
-    <t>2025 Q2</t>
-  </si>
-  <si>
-    <t>2025 Q3</t>
-  </si>
-  <si>
-    <t>2025 Q4</t>
-  </si>
-  <si>
-    <t>2026 Q1</t>
-  </si>
-  <si>
-    <t>2026 Q2</t>
-  </si>
-  <si>
-    <t>2026 Q3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Mean, </t>
-  </si>
-  <si>
-    <t>Table 3:  Computation of the Estimate of the Random 
+    <t>Table 4: Computation of Seasonally Adjusted Factors,</t>
+  </si>
+  <si>
+    <t>Table 5:  Computation of the Estimate of the Random 
 Component and the Seasonally Adjusted Time Series</t>
   </si>
 </sst>
@@ -1461,7 +1461,7 @@
                       <m:accPr>
                         <m:chr m:val="̅"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -2174,7 +2174,7 @@
                       <m:accPr>
                         <m:chr m:val="̿"/>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1400" i="1">
+                          <a:rPr lang="en-US" sz="1400" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
@@ -3566,7 +3566,7 @@
   <sheetData>
     <row r="1" spans="1:21" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -3622,7 +3622,7 @@
         <v>3.52</v>
       </c>
       <c r="C5" s="12">
-        <f t="shared" ref="C5:C86" si="0">(0.5*B3+SUM(B4:B6)+0.5*B7)/4</f>
+        <f t="shared" ref="C5:C6" si="0">(0.5*B3+SUM(B4:B6)+0.5*B7)/4</f>
         <v>3.7651249999999998</v>
       </c>
       <c r="D5" s="13">
@@ -3643,7 +3643,7 @@
         <v>4.1869999999999994</v>
       </c>
       <c r="D6" s="13">
-        <f t="shared" ref="D6:D69" si="1">B6/C6</f>
+        <f t="shared" ref="D6" si="1">B6/C6</f>
         <v>0.87843324576068793</v>
       </c>
       <c r="U6"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B17" s="11">
         <v>7.5609999999999999</v>
@@ -3771,7 +3771,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B18" s="11">
         <v>11.52</v>
@@ -3782,7 +3782,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B19" s="11">
         <v>11.88</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="11">
         <v>9.0839999999999996</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B21" s="11">
         <v>9.734</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" s="11">
         <v>12.207000000000001</v>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B23" s="11">
         <v>15.683</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24" s="11">
         <v>13.499000000000001</v>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B25" s="11">
         <v>15.7</v>
@@ -3859,7 +3859,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" s="11">
         <v>20.343</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B27" s="11">
         <v>26.741</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B28" s="11">
         <v>24.667000000000002</v>
@@ -3892,7 +3892,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B29" s="11">
         <v>28.571000000000002</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B30" s="11">
         <v>28.27</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B31" s="11">
         <v>46.332999999999998</v>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B32" s="11">
         <v>39.186</v>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B33" s="11">
         <v>35.023000000000003</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B34" s="11">
         <v>35.966000000000001</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B35" s="11">
         <v>54.512</v>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B36" s="11">
         <v>43.603000000000002</v>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B37" s="11">
         <v>35.323</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B38" s="11">
         <v>37.472000000000001</v>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B39" s="11">
         <v>57.594000000000001</v>
@@ -4013,7 +4013,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B40" s="11">
         <v>45.646000000000001</v>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B41" s="11">
         <v>37.432000000000002</v>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B42" s="11">
         <v>42.122999999999998</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B43" s="11">
         <v>74.599000000000004</v>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B44" s="11">
         <v>58.01</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B45" s="11">
         <v>49.604999999999997</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B46" s="11">
         <v>51.500999999999998</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B47" s="11">
         <v>75.872</v>
@@ -4101,7 +4101,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B48" s="11">
         <v>50.557000000000002</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B49" s="11">
         <v>42.357999999999997</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B50" s="11">
         <v>46.851999999999997</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B51" s="11">
         <v>78.350999999999999</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B52" s="11">
         <v>52.896000000000001</v>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B53" s="11">
         <v>45.408000000000001</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B54" s="11">
         <v>52.579000000000001</v>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B55" s="11">
         <v>88.293000000000006</v>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B56" s="11">
         <v>61.137</v>
@@ -4200,7 +4200,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B57" s="11">
         <v>53.265000000000001</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B58" s="11">
         <v>62.9</v>
@@ -4222,7 +4222,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B59" s="11">
         <v>84.31</v>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B60" s="11">
         <v>58.015000000000001</v>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B61" s="11">
         <v>53.808999999999997</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B62" s="11">
         <v>64.040000000000006</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B63" s="11">
         <v>91.819000000000003</v>
@@ -4277,7 +4277,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B64" s="11">
         <v>58.313000000000002</v>
@@ -4288,7 +4288,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B65" s="11">
         <v>59.685000000000002</v>
@@ -4299,7 +4299,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B66" s="11">
         <v>64.697999999999993</v>
@@ -4310,7 +4310,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B67" s="11">
         <v>111.43899999999999</v>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" s="11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B68" s="11">
         <v>89.584000000000003</v>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B69" s="11">
         <v>81.433999999999997</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B70" s="11">
         <v>83.36</v>
@@ -4354,7 +4354,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B71" s="11">
         <v>123.94499999999999</v>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B72" s="11">
         <v>97.278000000000006</v>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B73" s="11">
         <v>82.959000000000003</v>
@@ -4442,7 +4442,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B79" s="11">
         <v>119.575</v>
@@ -4453,7 +4453,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B80" s="11">
         <v>90.753</v>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B81" s="11">
         <v>85.777000000000001</v>
@@ -4475,7 +4475,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A82" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B82" s="11">
         <v>94.93</v>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B83" s="11">
         <v>124.3</v>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B84" s="11">
         <v>95.358999999999995</v>
@@ -4508,7 +4508,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B85" s="11">
         <v>94.036000000000001</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A86" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B86" s="11">
         <v>102.46599999999999</v>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B87" s="11">
         <v>143.756</v>
@@ -4541,7 +4541,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B88" s="11">
         <v>111.184</v>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B89" s="11">
         <v>109.417</v>
@@ -4563,19 +4563,19 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="U90"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="U91"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" s="27" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="B92" s="28"/>
       <c r="C92" s="28"/>
@@ -4888,7 +4888,7 @@
       <c r="D116" s="17"/>
       <c r="E116" s="17"/>
       <c r="F116" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
@@ -6083,7 +6083,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A187" s="20" t="str">
-        <f t="shared" ref="A187:A218" si="6">A67</f>
+        <f t="shared" ref="A187:A209" si="6">A67</f>
         <v>2021 Q1</v>
       </c>
       <c r="B187" s="20">
@@ -6104,7 +6104,7 @@
         <v>2021 Q2</v>
       </c>
       <c r="B188" s="20">
-        <f t="shared" ref="B188:D209" si="7">IF(LEN(B68)&gt;0,B68,"")</f>
+        <f t="shared" ref="B188:B209" si="7">IF(LEN(B68)&gt;0,B68,"")</f>
         <v>89.584000000000003</v>
       </c>
       <c r="C188" s="8"/>
@@ -6497,6 +6497,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -6691,38 +6708,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
-    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6745,9 +6734,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
+    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/handouts/chapter_1_5_handout.xlsx
+++ b/docs/handouts/chapter_1_5_handout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D827B22-62B8-48ED-81D3-A13987247CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AF1776-9407-41A2-919F-FADCE73D2F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="103">
   <si>
     <t>Year</t>
   </si>
@@ -4664,221 +4664,306 @@
       <c r="A99" s="15">
         <v>2010</v>
       </c>
-      <c r="B99" s="7" t="str" cm="1">
-        <f t="array" ref="B99">IF(LEN(D23)&gt;0,TRANSPOSE(D23:D26),"")</f>
-        <v/>
-      </c>
-      <c r="C99" s="7"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
+      <c r="B99" s="7">
+        <v>1.1594277898939118</v>
+      </c>
+      <c r="C99" s="7">
+        <v>0.88290792550321306</v>
+      </c>
+      <c r="D99" s="6">
+        <v>0.8875823275009187</v>
+      </c>
+      <c r="E99" s="6">
+        <v>0.99395360768075047</v>
+      </c>
       <c r="U99"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100" s="15">
         <v>2011</v>
       </c>
-      <c r="B100" s="7" t="str" cm="1">
-        <f t="array" ref="B100">IF(LEN(D27)&gt;0,TRANSPOSE(D27:D30),"")</f>
-        <v/>
-      </c>
-      <c r="C100" s="7"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
+      <c r="B100" s="7">
+        <v>1.1392905263270012</v>
+      </c>
+      <c r="C100" s="7">
+        <v>0.94613345095914592</v>
+      </c>
+      <c r="D100" s="6">
+        <v>0.96813926892286839</v>
+      </c>
+      <c r="E100" s="6">
+        <v>0.83700652477229909</v>
+      </c>
       <c r="U100"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" s="15">
         <v>2012</v>
       </c>
-      <c r="B101" s="7" t="str" cm="1">
-        <f t="array" ref="B101">IF(LEN(D31)&gt;0,TRANSPOSE(D31:D34),"")</f>
-        <v/>
-      </c>
-      <c r="C101" s="7"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
+      <c r="B101" s="7">
+        <v>1.2730070199057599</v>
+      </c>
+      <c r="C101" s="7">
+        <v>1.0267522599240142</v>
+      </c>
+      <c r="D101" s="6">
+        <v>0.8723174395616371</v>
+      </c>
+      <c r="E101" s="6">
+        <v>0.86200047335009033</v>
+      </c>
       <c r="U101"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" s="15">
         <v>2013</v>
       </c>
-      <c r="B102" s="7" t="str" cm="1">
-        <f t="array" ref="B102">IF(LEN(D35)&gt;0,TRANSPOSE(D35:D38),"")</f>
-        <v/>
-      </c>
-      <c r="C102" s="7"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
+      <c r="B102" s="7">
+        <v>1.2882886076547673</v>
+      </c>
+      <c r="C102" s="7">
+        <v>1.0250063176948347</v>
+      </c>
+      <c r="D102" s="6">
+        <v>0.81931679143640801</v>
+      </c>
+      <c r="E102" s="6">
+        <v>0.85643678916197885</v>
+      </c>
       <c r="U102"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" s="15">
         <v>2014</v>
       </c>
-      <c r="B103" s="7" t="str" cm="1">
-        <f t="array" ref="B103">IF(LEN(D39)&gt;0,TRANSPOSE(D39:D42),"")</f>
-        <v/>
-      </c>
-      <c r="C103" s="7"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
+      <c r="B103" s="7">
+        <v>1.3009015215470145</v>
+      </c>
+      <c r="C103" s="7">
+        <v>1.0117166612640918</v>
+      </c>
+      <c r="D103" s="6">
+        <v>0.78269710790783997</v>
+      </c>
+      <c r="E103" s="6">
+        <v>0.81799380528395682</v>
+      </c>
       <c r="U103"/>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" s="15">
         <v>2015</v>
       </c>
-      <c r="B104" s="7" t="str" cm="1">
-        <f t="array" ref="B104">IF(LEN(D43)&gt;0,TRANSPOSE(D43:D46),"")</f>
-        <v/>
-      </c>
-      <c r="C104" s="7"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
+      <c r="B104" s="7">
+        <v>1.367217944517882</v>
+      </c>
+      <c r="C104" s="7">
+        <v>1.0131600778950862</v>
+      </c>
+      <c r="D104" s="6">
+        <v>0.84667689346985187</v>
+      </c>
+      <c r="E104" s="6">
+        <v>0.89078380967000548</v>
+      </c>
       <c r="U104"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" s="15">
         <v>2016</v>
       </c>
-      <c r="B105" s="7" t="str" cm="1">
-        <f t="array" ref="B105">IF(LEN(D47)&gt;0,TRANSPOSE(D47:D50),"")</f>
-        <v/>
-      </c>
-      <c r="C105" s="7"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
+      <c r="B105" s="7">
+        <v>1.3553926439687107</v>
+      </c>
+      <c r="C105" s="7">
+        <v>0.92780671993246588</v>
+      </c>
+      <c r="D105" s="6">
+        <v>0.78123004354972936</v>
+      </c>
+      <c r="E105" s="6">
+        <v>0.85462235649546825</v>
+      </c>
       <c r="U105"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" s="15">
         <v>2017</v>
       </c>
-      <c r="B106" s="7" t="str" cm="1">
-        <f t="array" ref="B106">IF(LEN(D51)&gt;0,TRANSPOSE(D51:D54),"")</f>
-        <v/>
-      </c>
-      <c r="C106" s="7"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
+      <c r="B106" s="7">
+        <v>1.4118442035840744</v>
+      </c>
+      <c r="C106" s="7">
+        <v>0.93468009303332367</v>
+      </c>
+      <c r="D106" s="6">
+        <v>0.77552571465169395</v>
+      </c>
+      <c r="E106" s="6">
+        <v>0.86444317941277415</v>
+      </c>
       <c r="U106"/>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" s="15">
         <v>2018</v>
       </c>
-      <c r="B107" s="7" t="str" cm="1">
-        <f t="array" ref="B107">IF(LEN(D55)&gt;0,TRANSPOSE(D55:D58),"")</f>
-        <v/>
-      </c>
-      <c r="C107" s="7"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
+      <c r="B107" s="7">
+        <v>1.405125613945744</v>
+      </c>
+      <c r="C107" s="7">
+        <v>0.93900001727881666</v>
+      </c>
+      <c r="D107" s="6">
+        <v>0.80825937440132622</v>
+      </c>
+      <c r="E107" s="6">
+        <v>0.96750252835020822</v>
+      </c>
       <c r="U107"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" s="15">
         <v>2019</v>
       </c>
-      <c r="B108" s="7" t="str" cm="1">
-        <f t="array" ref="B108">IF(LEN(D59)&gt;0,TRANSPOSE(D59:D62),"")</f>
-        <v/>
-      </c>
-      <c r="C108" s="7"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
+      <c r="B108" s="7">
+        <v>1.3032825530796639</v>
+      </c>
+      <c r="C108" s="7">
+        <v>0.89389993990847605</v>
+      </c>
+      <c r="D108" s="6">
+        <v>0.81550874573984999</v>
+      </c>
+      <c r="E108" s="6">
+        <v>0.95642044266555171</v>
+      </c>
       <c r="U108"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" s="15">
         <v>2020</v>
       </c>
-      <c r="B109" s="7" t="str" cm="1">
-        <f t="array" ref="B109">IF(LEN(D63)&gt;0,TRANSPOSE(D63:D66),"")</f>
-        <v/>
-      </c>
-      <c r="C109" s="7"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
+      <c r="B109" s="7">
+        <v>1.3556671920389491</v>
+      </c>
+      <c r="C109" s="7">
+        <v>0.85070718417424662</v>
+      </c>
+      <c r="D109" s="6">
+        <v>0.83967290952255347</v>
+      </c>
+      <c r="E109" s="6">
+        <v>0.83543139194984672</v>
+      </c>
       <c r="U109"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" s="15">
         <v>2021</v>
       </c>
-      <c r="B110" s="7" t="str" cm="1">
-        <f t="array" ref="B110">IF(LEN(D67)&gt;0,TRANSPOSE(D67:D70),"")</f>
-        <v/>
-      </c>
-      <c r="C110" s="7"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
+      <c r="B110" s="7">
+        <v>1.3255481658912724</v>
+      </c>
+      <c r="C110" s="7">
+        <v>1.0051895446104475</v>
+      </c>
+      <c r="D110" s="6">
+        <v>0.87546966968581197</v>
+      </c>
+      <c r="E110" s="6">
+        <v>0.87249129968338701</v>
+      </c>
       <c r="U110"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" s="15">
         <v>2022</v>
       </c>
-      <c r="B111" s="7" t="str" cm="1">
-        <f t="array" ref="B111">IF(LEN(D71)&gt;0,TRANSPOSE(D71:D74),"")</f>
-        <v/>
-      </c>
-      <c r="C111" s="7"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
+      <c r="B111" s="7">
+        <v>1.2818156081178036</v>
+      </c>
+      <c r="C111" s="7">
+        <v>0.99533682069909324</v>
+      </c>
+      <c r="D111" s="6">
+        <v>0.84883195948149615</v>
+      </c>
+      <c r="E111" s="6">
+        <v>0.93339131695296074</v>
+      </c>
       <c r="U111"/>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" s="15">
         <v>2023</v>
       </c>
-      <c r="B112" s="7" t="str" cm="1">
-        <f t="array" ref="B112">IF(LEN(D75)&gt;0,TRANSPOSE(D75:D78),"")</f>
-        <v/>
-      </c>
-      <c r="C112" s="7"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
+      <c r="B112" s="7">
+        <v>1.2187228553446687</v>
+      </c>
+      <c r="C112" s="7">
+        <v>0.98888190840152335</v>
+      </c>
+      <c r="D112" s="6">
+        <v>0.85095404237500827</v>
+      </c>
+      <c r="E112" s="6">
+        <v>0.93308606868761634</v>
+      </c>
       <c r="U112"/>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" s="15">
         <v>2024</v>
       </c>
-      <c r="B113" s="7" t="str" cm="1">
-        <f t="array" ref="B113">IF(LEN(D79)&gt;0,TRANSPOSE(D79:D82),"")</f>
-        <v/>
-      </c>
-      <c r="C113" s="7"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
+      <c r="B113" s="7">
+        <v>1.2468294870090428</v>
+      </c>
+      <c r="C113" s="7">
+        <v>0.93482935421650737</v>
+      </c>
+      <c r="D113" s="6">
+        <v>0.87216619322695232</v>
+      </c>
+      <c r="E113" s="6">
+        <v>0.95391935447404053</v>
+      </c>
       <c r="U113"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" s="15">
         <v>2025</v>
       </c>
-      <c r="B114" s="7" t="str" cm="1">
-        <f t="array" ref="B114">IF(LEN(D83)&gt;0,TRANSPOSE(D83:D86),"")</f>
-        <v/>
-      </c>
-      <c r="C114" s="7"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
+      <c r="B114" s="7">
+        <v>1.2291854915567664</v>
+      </c>
+      <c r="C114" s="7">
+        <v>0.92493325541413163</v>
+      </c>
+      <c r="D114" s="6">
+        <v>0.88319726501506268</v>
+      </c>
+      <c r="E114" s="6">
+        <v>0.92409636788533778</v>
+      </c>
       <c r="U114"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" s="15">
         <v>2026</v>
       </c>
-      <c r="B115" s="7" t="str" cm="1">
-        <f t="array" ref="B115">IF(LEN(D87)&gt;0,TRANSPOSE(D87:D89),"")</f>
-        <v/>
-      </c>
-      <c r="C115" s="7"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
+      <c r="B115" s="7">
+        <v>1.2524140634784078</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="U115"/>
     </row>
     <row r="116" spans="1:21" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6497,23 +6582,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -6708,10 +6776,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
+    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6734,20 +6830,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
-    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/handouts/chapter_1_5_handout.xlsx
+++ b/docs/handouts/chapter_1_5_handout.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AF1776-9407-41A2-919F-FADCE73D2F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
+    <workbookView xWindow="3380" yWindow="3380" windowWidth="19200" windowHeight="11170" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Workbook" sheetId="2" r:id="rId1"/>
@@ -6582,6 +6582,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -6776,38 +6793,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
-    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6830,9 +6819,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
+    <ds:schemaRef ds:uri="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>